--- a/inst/shiny-examples/ContDataQC/rmd/tables/App_Information_Tables.xlsx
+++ b/inst/shiny-examples/ContDataQC/rmd/tables/App_Information_Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/ContDataQC/inst/shiny-examples/ContDataQC/rmd/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{42B4A4E6-2548-45D0-AD39-4BBAD99CD69A}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{678F0D11-7889-4DE0-B8FD-CBD6D2932B3F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview_Table1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="202">
   <si>
     <t>Main tab</t>
   </si>
@@ -89,21 +89,12 @@
     <t>Run functions</t>
   </si>
   <si>
-    <t>Drop-down menus for running the three main functions: QCRaw (which generates QC reports), Aggregate (which merges QC'd data files from the same site and different time periods together) and SummaryStats (which generates summary statistics and time series plots)</t>
-  </si>
-  <si>
     <t>Check input file</t>
   </si>
   <si>
     <t>Summary table showing what parameters are in the uploaded files; user should ensure all the desired parameters are present</t>
   </si>
   <si>
-    <t>Outputs</t>
-  </si>
-  <si>
-    <t>Examples of QC reports, aggregated data files and SummaryStats outputs</t>
-  </si>
-  <si>
     <t>Download USGS gage data</t>
   </si>
   <si>
@@ -119,18 +110,6 @@
     <t>Test Data</t>
   </si>
   <si>
-    <t>Streams</t>
-  </si>
-  <si>
-    <t>Test data files for streams (temperature, sensor depth, water level, water pressure, barometric pressure); sensors are deployed at a single depth at each site</t>
-  </si>
-  <si>
-    <t>Lakes</t>
-  </si>
-  <si>
-    <t>Test data files for lakes (temperature, DO and water level); sensors are deployed at multiple depths at each site</t>
-  </si>
-  <si>
     <t>FAQ</t>
   </si>
   <si>
@@ -138,9 +117,6 @@
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>ContDataQC is continually being improved; this page provides a status report and 'wish list' items that will be addressed as resources permit</t>
   </si>
   <si>
     <t>Folder name</t>
@@ -711,6 +687,21 @@
   </si>
   <si>
     <t>DO sensor data for a single depth</t>
+  </si>
+  <si>
+    <t>HOBOware Reformat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This function will automatically reformat CSV files for HOBO sensors so that they are ready to run through the QC function. In order for this function to work, users must follow specific formatting instructions when they export CSV files from HOBOware. </t>
+  </si>
+  <si>
+    <t>Run the three main functions: QCRaw (which generates QC reports), Aggregate (which merges QC'd data files from the same site and different time periods together) and SummaryStats (which generates summary statistics and time series plots). Includes instructions and examples of QC reports, aggregated data files and SummaryStats outputs.</t>
+  </si>
+  <si>
+    <t>Repository for test data files. There are two sets of folders: one with test data that can be run through the Shiny app or R package; the other with complete sets of outputs for each of the Test datasets so that the user can verify that the outputs that they generated during their test run(s) were complete.</t>
+  </si>
+  <si>
+    <t>ContDataQC is continually being improved; this page provides a status report and list of items that will be added as resources permit</t>
   </si>
 </sst>
 </file>
@@ -782,7 +773,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -826,16 +817,36 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
-      </right>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -846,7 +857,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -908,29 +919,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -944,8 +934,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1227,15 +1235,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="246.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1246,8 +1254,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3"/>
@@ -1255,8 +1263,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1266,8 +1274,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30"/>
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1275,8 +1283,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25"/>
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1284,118 +1292,101 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="31"/>
+      <c r="B6" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="27"/>
-      <c r="B7" s="5" t="s">
+    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="32"/>
+      <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
+    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="34"/>
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
-      <c r="B10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="29" t="s">
+    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="30"/>
-      <c r="B14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="6" t="s">
-        <v>36</v>
+      <c r="C15" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A13:A14"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1403,122 +1394,122 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFD92CEC-B8C0-47B9-A332-3F2BD5709CC7}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="100.77734375" style="9" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="100.7109375" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B6" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+    <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+    <row r="8" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B8" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="8" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="B10" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="8" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="8" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="B12" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+    <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B14" s="8" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1529,204 +1520,204 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53014024-6392-4EEB-A63C-6464C92A0508}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B1" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="24"/>
+      <c r="B3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="12" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="24"/>
+      <c r="B6" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C6" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="8" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24"/>
+      <c r="B7" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31"/>
-      <c r="B3" s="8" t="s">
+      <c r="C7" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="13" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="24"/>
+      <c r="B8" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
+      <c r="C8" t="s">
         <v>71</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24"/>
+      <c r="B9" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
-      <c r="B5" t="s">
+      <c r="C9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="31"/>
-      <c r="B6" t="s">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="24"/>
+      <c r="B10" t="s">
         <v>74</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="24"/>
+      <c r="B11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="31"/>
-      <c r="B7" t="s">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="24"/>
+      <c r="B12" t="s">
         <v>76</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="24"/>
+      <c r="B13" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="31"/>
-      <c r="B8" t="s">
+      <c r="C13" t="s">
         <v>78</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="24"/>
+      <c r="B14" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="31"/>
-      <c r="B9" t="s">
+      <c r="C14" t="s">
         <v>80</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="24"/>
+      <c r="B15" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="31"/>
-      <c r="B10" t="s">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24"/>
+      <c r="B16" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="31"/>
-      <c r="B11" t="s">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24"/>
+      <c r="B17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="31"/>
-      <c r="B12" t="s">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31"/>
-      <c r="B13" t="s">
+      <c r="B18" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C18" s="24" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
-      <c r="B14" t="s">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24"/>
+      <c r="B19" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C19" s="24"/>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="24"/>
+      <c r="B20" s="8" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="31"/>
-      <c r="B15" t="s">
+      <c r="C20" s="24" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
-      <c r="B16" t="s">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="24"/>
+      <c r="B21" s="8" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31"/>
-      <c r="B17" t="s">
+      <c r="C21" s="24"/>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24"/>
+      <c r="B22" s="8" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="31" t="s">
+      <c r="C22" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="8" t="s">
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="24"/>
+      <c r="B23" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C23" s="25"/>
+    </row>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24"/>
+      <c r="B24" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="31"/>
-      <c r="B19" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="31"/>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="31"/>
-      <c r="B20" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="31"/>
-      <c r="B21" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" s="31"/>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="31"/>
-      <c r="B22" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="31"/>
-      <c r="B23" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="32"/>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="31"/>
-      <c r="B24" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="32"/>
+      <c r="C24" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1744,50 +1735,50 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7288373-689A-4333-888E-9BEE47116881}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="170.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="170.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1798,516 +1789,504 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA83F796-74F9-475E-BD35-3C720D0E40EF}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B2" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="C2" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E2" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F2" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G2" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="G1" s="18" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="19" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="D3" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="E3" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="G3" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="E2" s="20" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="B4" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="D4" s="19" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="19" t="s">
+      <c r="E4" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="F4" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E5" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F5" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="21" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+      <c r="B6" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="C6" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E6" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="F6" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="F4" s="19" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="G4" s="21" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="D8" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="E5" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="19" t="s">
+      <c r="E9" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="E16" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="F16" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="F6" s="19" t="s">
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="D18" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" s="20" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="F23" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G23" s="22" t="s">
         <v>143</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="33"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="33"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="A22:A23"/>
@@ -2318,6 +2297,18 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2326,98 +2317,98 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3037767D-11B9-4D55-B076-80CDB032F77C}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="120.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="120.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="E2" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="35" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="B3" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="D3" s="8" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="E3" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="B2" s="8" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="B4" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="D4" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B5" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E5" s="13" t="s">
         <v>196</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/inst/shiny-examples/ContDataQC/rmd/tables/App_Information_Tables.xlsx
+++ b/inst/shiny-examples/ContDataQC/rmd/tables/App_Information_Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/ContDataQC/inst/shiny-examples/ContDataQC/rmd/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{678F0D11-7889-4DE0-B8FD-CBD6D2932B3F}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{510F0A4E-DF69-422F-8D6F-F3A70589B038}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview_Table1" sheetId="1" r:id="rId1"/>
@@ -195,6 +195,467 @@
   </si>
   <si>
     <t>If there is a nearby, representative weather station, we recommend comparing your sensor data to the weather station data as an additional QC check.</t>
+  </si>
+  <si>
+    <t>Column headings</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>SiteID</t>
+  </si>
+  <si>
+    <t>character (numeric or text)</t>
+  </si>
+  <si>
+    <t>Date Time</t>
+  </si>
+  <si>
+    <t>“Date Time” (one field) OR “Date” AND “Time” (in 2 separate fields) OR all 3 (in 3 fields); prefer 24H time (military); YYYY-MM-DD is recommended but not required</t>
+  </si>
+  <si>
+    <t>As available</t>
+  </si>
+  <si>
+    <t>Air Temp C</t>
+  </si>
+  <si>
+    <t>Water Temp C</t>
+  </si>
+  <si>
+    <t>Air BP psi</t>
+  </si>
+  <si>
+    <t>barometric pressure (BP)</t>
+  </si>
+  <si>
+    <t>Water P psi</t>
+  </si>
+  <si>
+    <t>water pressure (P)</t>
+  </si>
+  <si>
+    <t>Sensor Depth ft</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">differs from Water Level in that it is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>not</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> generated with a reference water level measurement</t>
+    </r>
+  </si>
+  <si>
+    <t>Water Level ft</t>
+  </si>
+  <si>
+    <t>generated with a reference water level (which relates water level to a fixed point)</t>
+  </si>
+  <si>
+    <t>Discharge ft3/s</t>
+  </si>
+  <si>
+    <t>Conductivity uS/cm</t>
+  </si>
+  <si>
+    <t>DO mg/L</t>
+  </si>
+  <si>
+    <t>DO adj mg/L</t>
+  </si>
+  <si>
+    <t>DO adjusted for salinity (HOBOware)</t>
+  </si>
+  <si>
+    <t>DO pctsat %</t>
+  </si>
+  <si>
+    <t>% saturation</t>
+  </si>
+  <si>
+    <t>pH SU</t>
+  </si>
+  <si>
+    <t>Turbidity NTU</t>
+  </si>
+  <si>
+    <t>Chlorophylla g/cm3</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t>Air LoggerID</t>
+  </si>
+  <si>
+    <t>unique identifier (e.g., serial number)</t>
+  </si>
+  <si>
+    <t>Water LoggerID</t>
+  </si>
+  <si>
+    <t>Water RowID</t>
+  </si>
+  <si>
+    <t>sequential number (1=first measurement; largest number = last measurement)</t>
+  </si>
+  <si>
+    <t>Air RowID</t>
+  </si>
+  <si>
+    <t>Discrete Water Temp C</t>
+  </si>
+  <si>
+    <t>Discrete (in situ) measurements can be entered into the row of the CSV file where the date/time of the sensor measurement most closely matches with the date/time of the field measurement; the data point(s) will be overlaid onto the time series plot in the QC report so that the user can visually check the correspondence between the two. Discrete entries can be made for any of the parameters listed above (not just temperature and water level)</t>
+  </si>
+  <si>
+    <t>Discrete Air Temp C</t>
+  </si>
+  <si>
+    <t>Discrete Water Level ft</t>
+  </si>
+  <si>
+    <t>Flag Test</t>
+  </si>
+  <si>
+    <t>Unrealistic values (‘Gross range’)</t>
+  </si>
+  <si>
+    <t>Entries are flagged if values are above or below upper and lower limits</t>
+  </si>
+  <si>
+    <t>Spikes</t>
+  </si>
+  <si>
+    <t>Entries are flagged if adjacent points change by more than ‘x’ amount</t>
+  </si>
+  <si>
+    <t>Rate of change (RoC)</t>
+  </si>
+  <si>
+    <t>Entries are flagged if the RoC exceeds a given threshold (e.g., ≥ 3 st dev within 25 hrs)</t>
+  </si>
+  <si>
+    <t>Flat line</t>
+  </si>
+  <si>
+    <t>Entries are flagged if a certain number of consecutive measurements are within a certain amount of each other (e.g., &gt;10 consecutive temperature measurements are within 0.01 degrees C of one another)</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Flag</t>
+  </si>
+  <si>
+    <t>Gross</t>
+  </si>
+  <si>
+    <t>Spike</t>
+  </si>
+  <si>
+    <t>Rate of Change</t>
+  </si>
+  <si>
+    <t>Flat Line</t>
+  </si>
+  <si>
+    <t>Temperature, Water</t>
+  </si>
+  <si>
+    <t>deg C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fail </t>
+  </si>
+  <si>
+    <t>&gt;30 or &lt;-2</t>
+  </si>
+  <si>
+    <t>≥1.5 (±)</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>&gt;30 consecutive measurements within 0.01 units of one another</t>
+  </si>
+  <si>
+    <t>Suspect</t>
+  </si>
+  <si>
+    <t>&gt;25 or &lt;-0.1</t>
+  </si>
+  <si>
+    <t>≥1.0 (±)</t>
+  </si>
+  <si>
+    <t>≥3 stdev within 25 hrs</t>
+  </si>
+  <si>
+    <t>&gt;20 consecutive measurements within 0.01 units of one another</t>
+  </si>
+  <si>
+    <t>Temperature, Air</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>&gt;38 or &lt;-25</t>
+  </si>
+  <si>
+    <t>≥10 (±)</t>
+  </si>
+  <si>
+    <t>&gt;35 or &lt;-23</t>
+  </si>
+  <si>
+    <t>≥8 (±)</t>
+  </si>
+  <si>
+    <t>&gt;15 consecutive measurements within 0.01 units of one another</t>
+  </si>
+  <si>
+    <t>Sensor Depth or Water Level</t>
+  </si>
+  <si>
+    <t>feet</t>
+  </si>
+  <si>
+    <t>&gt; 10^5 or &lt; -1</t>
+  </si>
+  <si>
+    <t>≥5  (±)</t>
+  </si>
+  <si>
+    <t>&gt;60 consecutive measurements within 0 units of one another</t>
+  </si>
+  <si>
+    <t>&gt; 1000 or &lt; 1</t>
+  </si>
+  <si>
+    <t>≥3  (±)</t>
+  </si>
+  <si>
+    <t>&gt;20 consecutive measurements within 0 units of one another</t>
+  </si>
+  <si>
+    <t>Discharge</t>
+  </si>
+  <si>
+    <t>ft3/s</t>
+  </si>
+  <si>
+    <t>≥10^4  (±)</t>
+  </si>
+  <si>
+    <t>&gt; 60 consecutive measurements within 0.01 units of one another</t>
+  </si>
+  <si>
+    <t>≥10^3  (±)</t>
+  </si>
+  <si>
+    <t>&gt; 30 consecutive measurements within 0.01 units of one another</t>
+  </si>
+  <si>
+    <t>Dissolved oxygen</t>
+  </si>
+  <si>
+    <t>mg/L</t>
+  </si>
+  <si>
+    <t>&gt; 20 or &lt; 1</t>
+  </si>
+  <si>
+    <t>&gt;= 10 (±)</t>
+  </si>
+  <si>
+    <t>&gt; 18 or &lt; 2</t>
+  </si>
+  <si>
+    <t>&gt;= 5 (±)</t>
+  </si>
+  <si>
+    <t>Conductivity</t>
+  </si>
+  <si>
+    <t>uS/cm</t>
+  </si>
+  <si>
+    <t>&gt; 1500 or &lt; 10</t>
+  </si>
+  <si>
+    <t>&gt;1200 or &lt; 20</t>
+  </si>
+  <si>
+    <t>pH</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>&gt; 12 or &lt; 3</t>
+  </si>
+  <si>
+    <t>&gt; 11 or &lt; 4</t>
+  </si>
+  <si>
+    <t>Turbidity</t>
+  </si>
+  <si>
+    <t>NTU</t>
+  </si>
+  <si>
+    <t>&gt; 1000 or &lt; -1</t>
+  </si>
+  <si>
+    <t>Pressure, Water</t>
+  </si>
+  <si>
+    <t>psi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;17  or &lt;13 </t>
+  </si>
+  <si>
+    <t>≥0.7  (±)</t>
+  </si>
+  <si>
+    <t>&gt;15 consecutive measurements within 0.001 units of one another</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;16.8  or &lt;13.5 </t>
+  </si>
+  <si>
+    <t>≥0.5  (±)</t>
+  </si>
+  <si>
+    <t>&gt;10 consecutive measurements within 0.001 units of one another</t>
+  </si>
+  <si>
+    <t>Barometric Pressure, Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;15  or &lt;13 </t>
+  </si>
+  <si>
+    <t>≥0.25  (±)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;14.8  or &lt;13 </t>
+  </si>
+  <si>
+    <t>≥0.15  (±)</t>
+  </si>
+  <si>
+    <t>Chlorophyll a</t>
+  </si>
+  <si>
+    <t>g/cm3</t>
+  </si>
+  <si>
+    <t>File name</t>
+  </si>
+  <si>
+    <t>Waterbody type</t>
+  </si>
+  <si>
+    <t>Parameter(s)</t>
+  </si>
+  <si>
+    <t>Sensor type</t>
+  </si>
+  <si>
+    <t>Data description</t>
+  </si>
+  <si>
+    <t>Hunting_AWTemp</t>
+  </si>
+  <si>
+    <t>Stream</t>
+  </si>
+  <si>
+    <t>Water and air temperature</t>
+  </si>
+  <si>
+    <t>Onset HOBO U22 (Pro v2)</t>
+  </si>
+  <si>
+    <t>Air and water temperature were collected with separate sensors but brought together into one file in HOBOware</t>
+  </si>
+  <si>
+    <t>QB283_AWTempWaterLevel</t>
+  </si>
+  <si>
+    <t>Water and air temperature, water and air pressure, water level</t>
+  </si>
+  <si>
+    <t>Onset HOBO U20</t>
+  </si>
+  <si>
+    <t>Data from two non vented pressure transducers (one on land, one in the water) were brought together in HOBOware Pro to generate water level</t>
+  </si>
+  <si>
+    <t>RUSS_WTempMultiDepth</t>
+  </si>
+  <si>
+    <t>Lake</t>
+  </si>
+  <si>
+    <t>Water temperature</t>
+  </si>
+  <si>
+    <t>Temperature sensors were deployed throughout the water column (at 1-m intervals). This dataset include temperature data for multiple depths</t>
+  </si>
+  <si>
+    <t>RUSS_DO</t>
+  </si>
+  <si>
+    <t>Onset HOBO U26</t>
+  </si>
+  <si>
+    <t>DO sensor data for a single depth</t>
+  </si>
+  <si>
+    <t>HOBOware Reformat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This function will automatically reformat CSV files for HOBO sensors so that they are ready to run through the QC function. In order for this function to work, users must follow specific formatting instructions when they export CSV files from HOBOware. </t>
+  </si>
+  <si>
+    <t>Run the three main functions: QCRaw (which generates QC reports), Aggregate (which merges QC'd data files from the same site and different time periods together) and SummaryStats (which generates summary statistics and time series plots). Includes instructions and examples of QC reports, aggregated data files and SummaryStats outputs.</t>
+  </si>
+  <si>
+    <t>Repository for test data files. There are two sets of folders: one with test data that can be run through the Shiny app or R package; the other with complete sets of outputs for each of the Test datasets so that the user can verify that the outputs that they generated during their test run(s) were complete.</t>
+  </si>
+  <si>
+    <t>ContDataQC is continually being improved; this page provides a status report and list of items that will be added as resources permit</t>
   </si>
   <si>
     <r>
@@ -239,469 +700,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[(click here to download an example worksheet).](https://github.com/leppott/ContDataQC/tree/dev_shinymods/Documents/Organizing_Files)</t>
+      <t>[(click here to download an example worksheet).](https://github.com/Blocktt/ShinyAppDocuments/tree/main/ContDataQC/Organizing_Files)</t>
     </r>
-  </si>
-  <si>
-    <t>Column headings</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Required</t>
-  </si>
-  <si>
-    <t>SiteID</t>
-  </si>
-  <si>
-    <t>character (numeric or text)</t>
-  </si>
-  <si>
-    <t>Date Time</t>
-  </si>
-  <si>
-    <t>“Date Time” (one field) OR “Date” AND “Time” (in 2 separate fields) OR all 3 (in 3 fields); prefer 24H time (military); YYYY-MM-DD is recommended but not required</t>
-  </si>
-  <si>
-    <t>As available</t>
-  </si>
-  <si>
-    <t>Air Temp C</t>
-  </si>
-  <si>
-    <t>Water Temp C</t>
-  </si>
-  <si>
-    <t>Air BP psi</t>
-  </si>
-  <si>
-    <t>barometric pressure (BP)</t>
-  </si>
-  <si>
-    <t>Water P psi</t>
-  </si>
-  <si>
-    <t>water pressure (P)</t>
-  </si>
-  <si>
-    <t>Sensor Depth ft</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">differs from Water Level in that it is </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>not</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> generated with a reference water level measurement</t>
-    </r>
-  </si>
-  <si>
-    <t>Water Level ft</t>
-  </si>
-  <si>
-    <t>generated with a reference water level (which relates water level to a fixed point)</t>
-  </si>
-  <si>
-    <t>Discharge ft3/s</t>
-  </si>
-  <si>
-    <t>Conductivity uS/cm</t>
-  </si>
-  <si>
-    <t>DO mg/L</t>
-  </si>
-  <si>
-    <t>DO adj mg/L</t>
-  </si>
-  <si>
-    <t>DO adjusted for salinity (HOBOware)</t>
-  </si>
-  <si>
-    <t>DO pctsat %</t>
-  </si>
-  <si>
-    <t>% saturation</t>
-  </si>
-  <si>
-    <t>pH SU</t>
-  </si>
-  <si>
-    <t>Turbidity NTU</t>
-  </si>
-  <si>
-    <t>Chlorophylla g/cm3</t>
-  </si>
-  <si>
-    <t>Optional</t>
-  </si>
-  <si>
-    <t>Air LoggerID</t>
-  </si>
-  <si>
-    <t>unique identifier (e.g., serial number)</t>
-  </si>
-  <si>
-    <t>Water LoggerID</t>
-  </si>
-  <si>
-    <t>Water RowID</t>
-  </si>
-  <si>
-    <t>sequential number (1=first measurement; largest number = last measurement)</t>
-  </si>
-  <si>
-    <t>Air RowID</t>
-  </si>
-  <si>
-    <t>Discrete Water Temp C</t>
-  </si>
-  <si>
-    <t>Discrete (in situ) measurements can be entered into the row of the CSV file where the date/time of the sensor measurement most closely matches with the date/time of the field measurement; the data point(s) will be overlaid onto the time series plot in the QC report so that the user can visually check the correspondence between the two. Discrete entries can be made for any of the parameters listed above (not just temperature and water level)</t>
-  </si>
-  <si>
-    <t>Discrete Air Temp C</t>
-  </si>
-  <si>
-    <t>Discrete Water Level ft</t>
-  </si>
-  <si>
-    <t>Flag Test</t>
-  </si>
-  <si>
-    <t>Unrealistic values (‘Gross range’)</t>
-  </si>
-  <si>
-    <t>Entries are flagged if values are above or below upper and lower limits</t>
-  </si>
-  <si>
-    <t>Spikes</t>
-  </si>
-  <si>
-    <t>Entries are flagged if adjacent points change by more than ‘x’ amount</t>
-  </si>
-  <si>
-    <t>Rate of change (RoC)</t>
-  </si>
-  <si>
-    <t>Entries are flagged if the RoC exceeds a given threshold (e.g., ≥ 3 st dev within 25 hrs)</t>
-  </si>
-  <si>
-    <t>Flat line</t>
-  </si>
-  <si>
-    <t>Entries are flagged if a certain number of consecutive measurements are within a certain amount of each other (e.g., &gt;10 consecutive temperature measurements are within 0.01 degrees C of one another)</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>Flag</t>
-  </si>
-  <si>
-    <t>Gross</t>
-  </si>
-  <si>
-    <t>Spike</t>
-  </si>
-  <si>
-    <t>Rate of Change</t>
-  </si>
-  <si>
-    <t>Flat Line</t>
-  </si>
-  <si>
-    <t>Temperature, Water</t>
-  </si>
-  <si>
-    <t>deg C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fail </t>
-  </si>
-  <si>
-    <t>&gt;30 or &lt;-2</t>
-  </si>
-  <si>
-    <t>≥1.5 (±)</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>&gt;30 consecutive measurements within 0.01 units of one another</t>
-  </si>
-  <si>
-    <t>Suspect</t>
-  </si>
-  <si>
-    <t>&gt;25 or &lt;-0.1</t>
-  </si>
-  <si>
-    <t>≥1.0 (±)</t>
-  </si>
-  <si>
-    <t>≥3 stdev within 25 hrs</t>
-  </si>
-  <si>
-    <t>&gt;20 consecutive measurements within 0.01 units of one another</t>
-  </si>
-  <si>
-    <t>Temperature, Air</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>&gt;38 or &lt;-25</t>
-  </si>
-  <si>
-    <t>≥10 (±)</t>
-  </si>
-  <si>
-    <t>&gt;35 or &lt;-23</t>
-  </si>
-  <si>
-    <t>≥8 (±)</t>
-  </si>
-  <si>
-    <t>&gt;15 consecutive measurements within 0.01 units of one another</t>
-  </si>
-  <si>
-    <t>Sensor Depth or Water Level</t>
-  </si>
-  <si>
-    <t>feet</t>
-  </si>
-  <si>
-    <t>&gt; 10^5 or &lt; -1</t>
-  </si>
-  <si>
-    <t>≥5  (±)</t>
-  </si>
-  <si>
-    <t>&gt;60 consecutive measurements within 0 units of one another</t>
-  </si>
-  <si>
-    <t>&gt; 1000 or &lt; 1</t>
-  </si>
-  <si>
-    <t>≥3  (±)</t>
-  </si>
-  <si>
-    <t>&gt;20 consecutive measurements within 0 units of one another</t>
-  </si>
-  <si>
-    <t>Discharge</t>
-  </si>
-  <si>
-    <t>ft3/s</t>
-  </si>
-  <si>
-    <t>≥10^4  (±)</t>
-  </si>
-  <si>
-    <t>&gt; 60 consecutive measurements within 0.01 units of one another</t>
-  </si>
-  <si>
-    <t>≥10^3  (±)</t>
-  </si>
-  <si>
-    <t>&gt; 30 consecutive measurements within 0.01 units of one another</t>
-  </si>
-  <si>
-    <t>Dissolved oxygen</t>
-  </si>
-  <si>
-    <t>mg/L</t>
-  </si>
-  <si>
-    <t>&gt; 20 or &lt; 1</t>
-  </si>
-  <si>
-    <t>&gt;= 10 (±)</t>
-  </si>
-  <si>
-    <t>&gt; 18 or &lt; 2</t>
-  </si>
-  <si>
-    <t>&gt;= 5 (±)</t>
-  </si>
-  <si>
-    <t>Conductivity</t>
-  </si>
-  <si>
-    <t>uS/cm</t>
-  </si>
-  <si>
-    <t>&gt; 1500 or &lt; 10</t>
-  </si>
-  <si>
-    <t>&gt;1200 or &lt; 20</t>
-  </si>
-  <si>
-    <t>pH</t>
-  </si>
-  <si>
-    <t>SU</t>
-  </si>
-  <si>
-    <t>&gt; 12 or &lt; 3</t>
-  </si>
-  <si>
-    <t>&gt; 11 or &lt; 4</t>
-  </si>
-  <si>
-    <t>Turbidity</t>
-  </si>
-  <si>
-    <t>NTU</t>
-  </si>
-  <si>
-    <t>&gt; 1000 or &lt; -1</t>
-  </si>
-  <si>
-    <t>Pressure, Water</t>
-  </si>
-  <si>
-    <t>psi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;17  or &lt;13 </t>
-  </si>
-  <si>
-    <t>≥0.7  (±)</t>
-  </si>
-  <si>
-    <t>&gt;15 consecutive measurements within 0.001 units of one another</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;16.8  or &lt;13.5 </t>
-  </si>
-  <si>
-    <t>≥0.5  (±)</t>
-  </si>
-  <si>
-    <t>&gt;10 consecutive measurements within 0.001 units of one another</t>
-  </si>
-  <si>
-    <t>Barometric Pressure, Air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;15  or &lt;13 </t>
-  </si>
-  <si>
-    <t>≥0.25  (±)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;14.8  or &lt;13 </t>
-  </si>
-  <si>
-    <t>≥0.15  (±)</t>
-  </si>
-  <si>
-    <t>Chlorophyll a</t>
-  </si>
-  <si>
-    <t>g/cm3</t>
-  </si>
-  <si>
-    <t>File name</t>
-  </si>
-  <si>
-    <t>Waterbody type</t>
-  </si>
-  <si>
-    <t>Parameter(s)</t>
-  </si>
-  <si>
-    <t>Sensor type</t>
-  </si>
-  <si>
-    <t>Data description</t>
-  </si>
-  <si>
-    <t>Hunting_AWTemp</t>
-  </si>
-  <si>
-    <t>Stream</t>
-  </si>
-  <si>
-    <t>Water and air temperature</t>
-  </si>
-  <si>
-    <t>Onset HOBO U22 (Pro v2)</t>
-  </si>
-  <si>
-    <t>Air and water temperature were collected with separate sensors but brought together into one file in HOBOware</t>
-  </si>
-  <si>
-    <t>QB283_AWTempWaterLevel</t>
-  </si>
-  <si>
-    <t>Water and air temperature, water and air pressure, water level</t>
-  </si>
-  <si>
-    <t>Onset HOBO U20</t>
-  </si>
-  <si>
-    <t>Data from two non vented pressure transducers (one on land, one in the water) were brought together in HOBOware Pro to generate water level</t>
-  </si>
-  <si>
-    <t>RUSS_WTempMultiDepth</t>
-  </si>
-  <si>
-    <t>Lake</t>
-  </si>
-  <si>
-    <t>Water temperature</t>
-  </si>
-  <si>
-    <t>Temperature sensors were deployed throughout the water column (at 1-m intervals). This dataset include temperature data for multiple depths</t>
-  </si>
-  <si>
-    <t>RUSS_DO</t>
-  </si>
-  <si>
-    <t>Onset HOBO U26</t>
-  </si>
-  <si>
-    <t>DO sensor data for a single depth</t>
-  </si>
-  <si>
-    <t>HOBOware Reformat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This function will automatically reformat CSV files for HOBO sensors so that they are ready to run through the QC function. In order for this function to work, users must follow specific formatting instructions when they export CSV files from HOBOware. </t>
-  </si>
-  <si>
-    <t>Run the three main functions: QCRaw (which generates QC reports), Aggregate (which merges QC'd data files from the same site and different time periods together) and SummaryStats (which generates summary statistics and time series plots). Includes instructions and examples of QC reports, aggregated data files and SummaryStats outputs.</t>
-  </si>
-  <si>
-    <t>Repository for test data files. There are two sets of folders: one with test data that can be run through the Shiny app or R package; the other with complete sets of outputs for each of the Test datasets so that the user can verify that the outputs that they generated during their test run(s) were complete.</t>
-  </si>
-  <si>
-    <t>ContDataQC is continually being improved; this page provides a status report and list of items that will be added as resources permit</t>
   </si>
 </sst>
 </file>
@@ -857,7 +857,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -883,7 +883,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -922,6 +921,27 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -934,26 +954,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1236,14 +1244,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.7109375" style="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1254,8 +1262,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3"/>
@@ -1263,8 +1271,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1274,8 +1282,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="25"/>
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1283,8 +1291,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="25"/>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1292,17 +1300,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
       <c r="B6" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1312,8 +1320,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="27"/>
       <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
@@ -1321,19 +1329,19 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="29"/>
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1341,7 +1349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1350,7 +1358,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
@@ -1359,16 +1367,16 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
@@ -1377,13 +1385,13 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -1397,118 +1405,118 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="100.7109375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="100.7109375" style="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="35" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:2" s="10" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="36" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="12" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1528,196 +1536,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="12" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="B2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="30"/>
+      <c r="B3" s="8" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24"/>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="13" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="B4" t="s">
         <v>63</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" t="s">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30"/>
+      <c r="B6" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>66</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="30"/>
+      <c r="B7" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>68</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="30"/>
+      <c r="B8" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24"/>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>70</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="30"/>
+      <c r="B9" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>72</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="30"/>
+      <c r="B10" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
-      <c r="B10" t="s">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
+      <c r="B11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" t="s">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="30"/>
+      <c r="B12" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" t="s">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="30"/>
+      <c r="B13" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>77</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="30"/>
+      <c r="B14" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>79</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="30"/>
+      <c r="B15" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" t="s">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="30"/>
+      <c r="B16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
-      <c r="B16" t="s">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
+      <c r="B17" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
-      <c r="B17" t="s">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="30" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+      <c r="B18" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="24" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="30"/>
+      <c r="B19" s="8" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="8" t="s">
+      <c r="C19" s="30"/>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="30"/>
+      <c r="B20" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="24"/>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="8" t="s">
+      <c r="C20" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="24" t="s">
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="30"/>
+      <c r="B21" s="8" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="8" t="s">
+      <c r="C21" s="30"/>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="30"/>
+      <c r="B22" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="24"/>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
-      <c r="B22" s="8" t="s">
+      <c r="C22" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="25" t="s">
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
+      <c r="B23" s="8" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
-      <c r="B23" s="8" t="s">
+      <c r="C23" s="31"/>
+    </row>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="30"/>
+      <c r="B24" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="25"/>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
-      <c r="B24" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" s="25"/>
+      <c r="C24" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1742,43 +1750,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="15" t="s">
+      <c r="A1" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="B3" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="B4" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="B5" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1801,492 +1809,504 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="G1" s="18" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="B2" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="C2" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="G2" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="G2" s="21" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="32"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="18" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="F3" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="G3" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="G3" s="21" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="B4" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="F4" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="32"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="E5" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="F5" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="21" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="B6" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="C6" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="E6" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="F6" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G6" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" s="21" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="32"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="E7" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="F7" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G7" s="21" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="B8" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="C8" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E8" s="20" t="s">
+      <c r="F8" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="F8" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="22" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="32"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" s="20" t="s">
+      <c r="F9" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G9" s="22" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
+      <c r="B10" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="C10" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D10" s="20" t="s">
+      <c r="E10" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="F10" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="32"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="F10" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G10" s="22" t="s">
+      <c r="E11" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="32"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="32"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="32"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17" s="19" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G12" s="22" t="s">
+      <c r="F17" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="32"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="32"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="32"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E23" s="19" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="E17" s="20" t="s">
+      <c r="F23" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" s="21" t="s">
         <v>142</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>143</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="A22:A23"/>
@@ -2297,18 +2317,6 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2327,88 +2335,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="C1" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="D1" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="E1" s="22" t="s">
         <v>179</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="12" t="s">
         <v>184</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="12" t="s">
         <v>188</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/inst/shiny-examples/ContDataQC/rmd/tables/App_Information_Tables.xlsx
+++ b/inst/shiny-examples/ContDataQC/rmd/tables/App_Information_Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/ContDataQC/inst/shiny-examples/ContDataQC/rmd/tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\OneDrive - Tetra Tech, Inc\MyDocs_OneDrive\GitHub\ContDataQC\inst\shiny-examples\ContDataQC\rmd\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{510F0A4E-DF69-422F-8D6F-F3A70589B038}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583B93C7-747E-42AB-9689-CAB3DE8D8D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview_Table1" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,26 @@
     <sheet name="QCThresh_Table3a2" sheetId="5" r:id="rId5"/>
     <sheet name="TestData_Table7" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="204">
   <si>
     <t>Main tab</t>
   </si>
@@ -41,9 +50,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
     <t>Purpose, funding, main uses to date</t>
   </si>
   <si>
@@ -83,9 +89,6 @@
     <t>Instructions on how to evaluate and adjust QC test thresholds</t>
   </si>
   <si>
-    <t>Main functions</t>
-  </si>
-  <si>
     <t>Run functions</t>
   </si>
   <si>
@@ -95,9 +98,6 @@
     <t>Summary table showing what parameters are in the uploaded files; user should ensure all the desired parameters are present</t>
   </si>
   <si>
-    <t>Download USGS gage data</t>
-  </si>
-  <si>
     <t>Download USGS gage data for desired sites and time periods</t>
   </si>
   <si>
@@ -110,9 +110,6 @@
     <t>Test Data</t>
   </si>
   <si>
-    <t>FAQ</t>
-  </si>
-  <si>
     <t>Frequently asked questions</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
     <t xml:space="preserve">Data0_Original </t>
   </si>
   <si>
-    <t>For files that are exported out of the sensor software (like HOBOWare) that need to be reformatted before they can be run through the ContDataQC R package.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data1_RAW </t>
   </si>
   <si>
@@ -155,40 +149,22 @@
     <t xml:space="preserve">FieldForms </t>
   </si>
   <si>
-    <t>Observations from site visits are very important for the QC process as they can provide clues as to why erroneous measurements or changes may have occurred (e.g., had to move sensor, sensor out of water, sensor buried in sediment, vandalism).</t>
-  </si>
-  <si>
     <t xml:space="preserve">in_situ </t>
   </si>
   <si>
     <t>orig</t>
   </si>
   <si>
-    <t>If you are overrun with raw files that are not named consistently and are poorly organized (for example, sometimes files are saved multiple times with different names and in different folders), RMN partners have found it helpful to put all the raw files for a site into one folder, inventory what they have, and then sort them into the appropriate folders.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Photos </t>
   </si>
   <si>
-    <t>RMN protocols call for taking photos from the same locations during each site visit. Photographs are important for relocating the sensors and documenting changes to the monitoring location.</t>
-  </si>
-  <si>
     <t xml:space="preserve">R_ConfigurationFiles </t>
   </si>
   <si>
-    <t>Creating a customized configuration file (or files) for a site allows you to adjust QC test thresholds, make changes to units and plot labels, and more. Under the 'QC Thresholds' tab, you can upload a customized configuration file. If the file is stored in this folder, it will be easy to find. The customized file needs to be uploaded before running the QC function, otherwise the default settings will be used.</t>
-  </si>
-  <si>
     <t>SensorFile</t>
   </si>
   <si>
-    <t xml:space="preserve">We recommend retaining original sensor files in case you need to go back and regenerate certain data (e.g., with HOBO sensors, sometimes people go back and rerun sensor depth with reference water level measurements). In some situations, it may be helpful to add subfolders for each sensor type (for example, with lakes, there may be many temperature files mixed in with DO and water level files; in these cases, it may be easier to find files if you create subfolders for temperature, DO and water level). </t>
-  </si>
-  <si>
     <t>USGSgage</t>
-  </si>
-  <si>
-    <t>If there is a nearby, representative USGS gage, we recommend comparing your sensor data to the USGS gage data as an additional QC check.</t>
   </si>
   <si>
     <t>WxStation</t>
@@ -310,27 +286,18 @@
     <t>Air LoggerID</t>
   </si>
   <si>
-    <t>unique identifier (e.g., serial number)</t>
-  </si>
-  <si>
     <t>Water LoggerID</t>
   </si>
   <si>
     <t>Water RowID</t>
   </si>
   <si>
-    <t>sequential number (1=first measurement; largest number = last measurement)</t>
-  </si>
-  <si>
     <t>Air RowID</t>
   </si>
   <si>
     <t>Discrete Water Temp C</t>
   </si>
   <si>
-    <t>Discrete (in situ) measurements can be entered into the row of the CSV file where the date/time of the sensor measurement most closely matches with the date/time of the field measurement; the data point(s) will be overlaid onto the time series plot in the QC report so that the user can visually check the correspondence between the two. Discrete entries can be made for any of the parameters listed above (not just temperature and water level)</t>
-  </si>
-  <si>
     <t>Discrete Air Temp C</t>
   </si>
   <si>
@@ -655,60 +622,65 @@
     <t>Repository for test data files. There are two sets of folders: one with test data that can be run through the Shiny app or R package; the other with complete sets of outputs for each of the Test datasets so that the user can verify that the outputs that they generated during their test run(s) were complete.</t>
   </si>
   <si>
-    <t>ContDataQC is continually being improved; this page provides a status report and list of items that will be added as resources permit</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">An important QC check (which we call an 'accuracy check') involves comparing </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>in situ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> measurements taken during site visits to the closest sensor measurement(s). We ask that RMN partners keep an accuracy check worksheet in this folder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[(click here to download an example worksheet).](https://github.com/Blocktt/ShinyAppDocuments/tree/main/ContDataQC/Organizing_Files)</t>
-    </r>
+    <t>About ContDataQC</t>
+  </si>
+  <si>
+    <t>Frequent Questions</t>
+  </si>
+  <si>
+    <t>Download USGS Gage Data</t>
+  </si>
+  <si>
+    <t>Main Functions</t>
+  </si>
+  <si>
+    <t>For .csv files that are exported out of the sensor software (like HOBOWare) that need to be reformatted before they can be run through the QC function.</t>
+  </si>
+  <si>
+    <t>Observations from site visits are very important for the QC process as they can provide clues as to why erroneous measurements or changes may have occurred (e.g., sensor movement, sensor out of water, sensor buried in sediment, vandalism).</t>
+  </si>
+  <si>
+    <t>An important QC check (which we call an ‘accuracy check’) involves comparing in situ measurements taken during site visits to the closest sensor measurement(s). We recommend keeping an accuracy check worksheet in this folder (click here to download an example worksheet).</t>
+  </si>
+  <si>
+    <t>If you are overrun with raw files that are not named consistently and are poorly organized (for example, sometimes files are saved multiple times with different names and in different folders), it may be helpful to put all the raw files for a site into one folder, inventory them, and then sort them into the appropriate folders.</t>
+  </si>
+  <si>
+    <t>We recommend taking photos from the same locations during each site visit. Photographs are important for relocating the sensors and documenting changes to the monitoring location.</t>
+  </si>
+  <si>
+    <t>Creating a customized configuration file (or files) for a site allows users to adjust QC test thresholds, make changes to units and more. The customized file needs to be uploaded before running the QC function, otherwise the default settings will be used.</t>
+  </si>
+  <si>
+    <t>We recommend retaining original sensor files in case you need to go back and regenerate certain data. In some situations, it may be helpful to add subfolders for each sensor type (for example, with lakes, there may be many temperature files mixed in with DO and water level files; in these cases, it may be easier to find files if you create subfolders for temperature, DO and water level).</t>
+  </si>
+  <si>
+    <t>If there is a nearby, representative USGS gage, we recommend comparing sensor hydrologic data to the USGS gage data as an additional QC check.</t>
+  </si>
+  <si>
+    <t>Salinity ppt</t>
+  </si>
+  <si>
+    <t>unique identifier (e.g., serial number) for sensor deployed on land</t>
+  </si>
+  <si>
+    <t>unique sensor identifier (e.g., serial number) for sensor deployed in the water</t>
+  </si>
+  <si>
+    <t>sequential record number (1=first measurement; largest number = last measurement) for sensor deployed in the water</t>
+  </si>
+  <si>
+    <t>sequential record number (1=first measurement; largest number = last measurement) for sensor deployed on land</t>
+  </si>
+  <si>
+    <t>Discrete (in situ) measurements can be entered into the row of the CSV file where the date/time of the sensor measurement most closely matches with the date/time of the in situ measurement; the data point(s) will be overlaid onto the time series plot in the QC report so that the user can visually check the correspondence between the two. Discrete entries can be made for any of the parameters listed above (not just the Water Temp C example shown here)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -735,13 +707,6 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -857,7 +822,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -909,13 +874,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -943,6 +908,18 @@
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -953,15 +930,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1243,12 +1211,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255.7109375" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.7109375" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1264,134 +1232,125 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
-        <v>3</v>
+        <v>186</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="25"/>
       <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="25"/>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="26"/>
+      <c r="B7" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="27"/>
+      <c r="B9" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="5" t="s">
+      <c r="C9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="C10" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="29"/>
+      <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="6" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -1405,119 +1364,119 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="100.7109375" style="34" customWidth="1"/>
+    <col min="2" max="2" width="100.7109375" style="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="31" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>31</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="10" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>201</v>
+        <v>36</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>50</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>52</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1527,214 +1486,222 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53014024-6392-4EEB-A63C-6464C92A0508}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="126" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="34"/>
+      <c r="B3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="34"/>
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34"/>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="11" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="34"/>
+      <c r="B7" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="C7" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="8" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="34"/>
+      <c r="B8" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="8" t="s">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="34"/>
+      <c r="B9" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="34"/>
+      <c r="B10" t="s">
         <v>62</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="34"/>
+      <c r="B11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" t="s">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="34"/>
+      <c r="B12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
-      <c r="B6" t="s">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" t="s">
         <v>65</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C13" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" t="s">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="34"/>
+      <c r="B14" t="s">
         <v>67</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C14" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" t="s">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="34"/>
+      <c r="B15" t="s">
         <v>69</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="34"/>
+      <c r="B16" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" t="s">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="34"/>
+      <c r="B17" t="s">
         <v>71</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="34"/>
+      <c r="B18" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="34" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" t="s">
+      <c r="B19" s="8" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" t="s">
+      <c r="C19" s="33" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="34"/>
+      <c r="B20" s="8" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
-      <c r="B12" t="s">
+      <c r="C20" s="33" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="34"/>
+      <c r="B21" s="8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" t="s">
+      <c r="C21" s="33" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="34"/>
+      <c r="B22" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C22" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="34"/>
+      <c r="B23" s="8" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
-      <c r="B14" t="s">
+      <c r="C23" s="35" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="34"/>
+      <c r="B24" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C24" s="35"/>
+    </row>
+    <row r="25" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="34"/>
+      <c r="B25" s="8" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30"/>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" s="30"/>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
-      <c r="B20" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="30"/>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
-      <c r="B22" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="31"/>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="30"/>
-      <c r="B24" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="31"/>
+      <c r="C25" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="A4:A18"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="C23:C25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1751,7 +1718,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>2</v>
@@ -1759,34 +1726,34 @@
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1810,487 +1777,487 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="D3" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="F3" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="G3" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="F1" s="17" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="B4" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="D4" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="E4" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="F4" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="E5" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="F5" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="F2" s="18" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="B6" s="37" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="32"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="18" t="s">
+      <c r="C6" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="E6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="F6" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="18" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="36"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="E7" s="19" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+      <c r="F7" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G7" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B4" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="18" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="B8" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="C8" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="F4" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="18" t="s">
+      <c r="F8" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="36"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="36"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="36"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E16" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="E5" s="19" t="s">
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="20" t="s">
+      <c r="F17" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="18" t="s">
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="36"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="36"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" s="19" t="s">
+      <c r="E22" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="36"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E10" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="32"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="32"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="32"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="B20" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="32"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="B22" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>159</v>
-      </c>
       <c r="E23" s="19" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2336,87 +2303,87 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
